--- a/historialFantasyV3.xlsx
+++ b/historialFantasyV3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\latuf\Downloads\FantasyLFA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\latuf\OneDrive\Desktop\FantasyLFA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1E63D5-6E4F-46CF-93B0-1692054033AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C07F0D5-DAEA-4F09-AE96-41ADBF64FD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partidos regular" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="182">
   <si>
     <t>Temporada</t>
   </si>
@@ -559,13 +557,40 @@
   </si>
   <si>
     <t>KJ</t>
+  </si>
+  <si>
+    <t>P= semis de playoffs</t>
+  </si>
+  <si>
+    <t>despues posiciones temporada regular</t>
+  </si>
+  <si>
+    <t>final en la F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 - 1 </t>
+  </si>
+  <si>
+    <t>Puntos 2025</t>
+  </si>
+  <si>
+    <t>: ultimo bloque</t>
+  </si>
+  <si>
+    <t>2026 -1</t>
+  </si>
+  <si>
+    <t>Puntos 2026</t>
+  </si>
+  <si>
+    <t>Nehue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,8 +607,22 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -626,6 +665,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -640,7 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -696,8 +753,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -986,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B435"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="6" bestFit="1" customWidth="1"/>
@@ -997,7 +1068,7 @@
         <v>96</v>
       </c>
       <c r="B1">
-        <v>73</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2655,7 +2726,7 @@
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A291" s="22" t="s">
+      <c r="A291" s="21" t="s">
         <v>64</v>
       </c>
       <c r="B291" t="s">
@@ -2663,22 +2734,22 @@
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A292" s="22" t="s">
+      <c r="A292" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A293" s="22" t="s">
+      <c r="A293" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A294" s="22" t="s">
+      <c r="A294" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A295" s="22" t="s">
+      <c r="A295" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B295">
@@ -2686,22 +2757,22 @@
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A296" s="22" t="s">
+      <c r="A296" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A297" s="22" t="s">
+      <c r="A297" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A298" s="22" t="s">
+      <c r="A298" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A299" s="22" t="s">
+      <c r="A299" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B299">
@@ -2709,22 +2780,22 @@
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A300" s="22" t="s">
+      <c r="A300" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A301" s="22" t="s">
+      <c r="A301" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A302" s="22" t="s">
+      <c r="A302" s="21" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A303" s="22" t="s">
+      <c r="A303" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B303">
@@ -2732,22 +2803,22 @@
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A304" s="22" t="s">
+      <c r="A304" s="21" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A305" s="22" t="s">
+      <c r="A305" s="21" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A306" s="22" t="s">
+      <c r="A306" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A307" s="22" t="s">
+      <c r="A307" s="21" t="s">
         <v>47</v>
       </c>
       <c r="B307">
@@ -2755,22 +2826,22 @@
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A308" s="22" t="s">
+      <c r="A308" s="21" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A309" s="22" t="s">
+      <c r="A309" s="21" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A310" s="22" t="s">
+      <c r="A310" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A311" s="22" t="s">
+      <c r="A311" s="21" t="s">
         <v>49</v>
       </c>
       <c r="B311">
@@ -2778,22 +2849,22 @@
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A312" s="22" t="s">
+      <c r="A312" s="21" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A313" s="22" t="s">
+      <c r="A313" s="21" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A314" s="22" t="s">
+      <c r="A314" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A315" s="22" t="s">
+      <c r="A315" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B315">
@@ -2801,22 +2872,22 @@
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A316" s="22" t="s">
+      <c r="A316" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A317" s="22" t="s">
+      <c r="A317" s="21" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A318" s="22" t="s">
+      <c r="A318" s="21" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A319" s="22" t="s">
+      <c r="A319" s="21" t="s">
         <v>71</v>
       </c>
       <c r="B319">
@@ -2824,22 +2895,22 @@
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A320" s="22" t="s">
+      <c r="A320" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A321" s="22" t="s">
+      <c r="A321" s="21" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A322" s="22" t="s">
+      <c r="A322" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A323" s="22" t="s">
+      <c r="A323" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B323">
@@ -2847,22 +2918,22 @@
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A324" s="22" t="s">
+      <c r="A324" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A325" s="22" t="s">
+      <c r="A325" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A326" s="22" t="s">
+      <c r="A326" s="21" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A327" s="22" t="s">
+      <c r="A327" s="21" t="s">
         <v>54</v>
       </c>
       <c r="B327">
@@ -2870,22 +2941,22 @@
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A328" s="22" t="s">
+      <c r="A328" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A329" s="22" t="s">
+      <c r="A329" s="21" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A330" s="22" t="s">
+      <c r="A330" s="21" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A331" s="22" t="s">
+      <c r="A331" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B331">
@@ -2893,22 +2964,22 @@
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A332" s="22" t="s">
+      <c r="A332" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A333" s="22" t="s">
+      <c r="A333" s="21" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A334" s="22" t="s">
+      <c r="A334" s="21" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A335" s="22" t="s">
+      <c r="A335" s="21" t="s">
         <v>55</v>
       </c>
       <c r="B335">
@@ -2916,22 +2987,22 @@
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A336" s="22" t="s">
+      <c r="A336" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A337" s="22" t="s">
+      <c r="A337" s="21" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A338" s="22" t="s">
+      <c r="A338" s="21" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A339" s="22" t="s">
+      <c r="A339" s="21" t="s">
         <v>50</v>
       </c>
       <c r="B339">
@@ -2939,22 +3010,22 @@
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A340" s="22" t="s">
+      <c r="A340" s="21" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A341" s="22" t="s">
+      <c r="A341" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A342" s="22" t="s">
+      <c r="A342" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A343" s="22" t="s">
+      <c r="A343" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B343">
@@ -2962,22 +3033,22 @@
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A344" s="22" t="s">
+      <c r="A344" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A345" s="22" t="s">
+      <c r="A345" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A346" s="22" t="s">
+      <c r="A346" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A347" s="22" t="s">
+      <c r="A347" s="21" t="s">
         <v>41</v>
       </c>
       <c r="B347">
@@ -2985,40 +3056,461 @@
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A348" s="22" t="s">
+      <c r="A348" s="21" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A349" s="22" t="s">
+      <c r="A349" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A350" s="22" t="s">
+      <c r="A350" s="21" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A351"/>
+      <c r="A351" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B351" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A352"/>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353"/>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354"/>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355"/>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A356"/>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A357"/>
+      <c r="A352" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A353" s="24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A354" s="24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A355" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B355">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A356" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A357" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A358" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A359" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B359">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A360" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A361" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A362" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A363" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B363">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A364" s="24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A365" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A366" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A367" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B367">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A368" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A369" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A370" s="24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A371" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B371">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A372" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A373" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A374" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A375" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B375">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A376" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A377" s="24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A378" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A379" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B379">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A380" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A381" s="24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A382" s="24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A383" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B383">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A384" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A385" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A386" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A387" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B387">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A388" s="24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A389" s="24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A390" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A391" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B391">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A392" s="24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A393" s="24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A394" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A395" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B395">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A396" s="24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A397" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A398" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A399" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B399">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A400" s="24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A401" s="24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A402" s="24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A403" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B403">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A404" s="24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A405" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A406" s="24" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A407" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B407">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A408" s="24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A409" s="24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A410" s="24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A411" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B411" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A412" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A413" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A414" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A415" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A416" s="26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="26" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="26"/>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="26"/>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="26"/>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="26"/>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="26"/>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="26"/>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="26"/>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="26"/>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="26"/>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="26"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="26"/>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="26"/>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="26"/>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="26"/>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="26"/>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="26"/>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3028,10 +3520,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -3048,12 +3540,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -3069,8 +3561,14 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>86</v>
       </c>
@@ -3080,8 +3578,11 @@
       <c r="E6" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>27</v>
       </c>
@@ -3098,7 +3599,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>54</v>
       </c>
@@ -3114,8 +3615,14 @@
       <c r="E8" s="18" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>2025</v>
+      </c>
+      <c r="I8" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>28</v>
       </c>
@@ -3132,7 +3639,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>53</v>
       </c>
@@ -3145,8 +3652,11 @@
       <c r="D10" s="12" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>10</v>
       </c>
@@ -3159,8 +3669,11 @@
       <c r="D11" s="19" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>68</v>
       </c>
@@ -3174,32 +3687,88 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>88</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="17" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3209,7 +3778,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3227,7 +3796,7 @@
       </c>
       <c r="B2">
         <f>COUNTIF('partidos regular'!A:A,"E*")</f>
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3236,7 +3805,7 @@
       </c>
       <c r="B3" s="15">
         <f>(B2/'partidos regular'!$B$1)*100</f>
-        <v>65.753424657534239</v>
+        <v>50.476190476190474</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3244,8 +3813,8 @@
         <v>94</v>
       </c>
       <c r="B4">
-        <f>SUM(B6:B12)</f>
-        <v>13270.68</v>
+        <f>SUM(B6:B13)</f>
+        <v>13288.24</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3254,7 +3823,7 @@
       </c>
       <c r="B5" s="14">
         <f>B4/'partidos regular'!$B$1</f>
-        <v>181.79013698630138</v>
+        <v>126.55466666666666</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3291,565 +3860,564 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="B10">
-        <v>2047.52</v>
+        <v>1873.52</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B11">
-        <v>1873.52</v>
+        <v>1812.42</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B12">
-        <v>1812.42</v>
+        <v>1744.1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>180</v>
+      </c>
+      <c r="B13">
+        <v>320.98</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14">
-        <f>COUNTIF('partidos regular'!A:A,"J*")</f>
-        <v>52</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="15">
-        <f>(B14/'partidos regular'!$B$1)*100</f>
-        <v>71.232876712328761</v>
+        <v>92</v>
+      </c>
+      <c r="B15">
+        <f>COUNTIF('partidos regular'!A:A,"J*")</f>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16">
-        <f>SUM(B18:B23)</f>
-        <v>11850.32</v>
+        <v>93</v>
+      </c>
+      <c r="B16" s="15">
+        <f>(B15/'partidos regular'!$B$1)*100</f>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="14">
-        <f>B16/'partidos regular'!$B$1</f>
-        <v>162.3331506849315</v>
+        <v>94</v>
+      </c>
+      <c r="B17">
+        <f>SUM(B19:B26)</f>
+        <v>14298.02</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18">
-        <v>1501.6</v>
+        <v>95</v>
+      </c>
+      <c r="B18" s="14">
+        <f>B17/'partidos regular'!$B$1</f>
+        <v>136.17161904761906</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19">
-        <v>1769.2</v>
+        <v>1501.6</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20">
-        <v>2237</v>
+        <v>1769.2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21">
-        <v>2036.44</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="B22">
-        <v>2083.06</v>
+        <v>2036.44</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B23">
-        <v>2223.02</v>
+        <v>2083.06</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>170</v>
+      </c>
+      <c r="B24">
+        <v>2223.02</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="B25">
-        <f>COUNTIF('partidos regular'!A:A,"L*")</f>
-        <v>43</v>
+        <v>2216.42</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="15">
-        <f>(B25/'partidos regular'!$B$1)*100</f>
-        <v>58.904109589041099</v>
+        <v>180</v>
+      </c>
+      <c r="B26">
+        <v>231.28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27">
-        <f>SUM(B29:B34)</f>
-        <v>11162.82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="14">
-        <f>B27/'partidos regular'!$B$1</f>
-        <v>152.91534246575341</v>
+        <v>92</v>
+      </c>
+      <c r="B28">
+        <f>COUNTIF('partidos regular'!A:A,"L*")</f>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29">
-        <v>1757.1</v>
+        <v>93</v>
+      </c>
+      <c r="B29" s="15">
+        <f>(B28/'partidos regular'!$B$1)*100</f>
+        <v>48.571428571428569</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B30">
-        <v>1815.4</v>
+        <f>SUM(B32:B39)</f>
+        <v>13372.72</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>99</v>
-      </c>
-      <c r="B31">
-        <v>1899.86</v>
+        <v>95</v>
+      </c>
+      <c r="B31" s="14">
+        <f>B30/'partidos regular'!$B$1</f>
+        <v>127.35923809523808</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B32">
-        <v>1750.04</v>
+        <v>1757.1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="B33">
-        <v>1860.94</v>
+        <v>1815.4</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="B34">
-        <v>2079.48</v>
+        <v>1899.86</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>100</v>
+      </c>
+      <c r="B35">
+        <v>1750.04</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="B36">
-        <f>COUNTIF('partidos regular'!A:A,"C*")</f>
-        <v>36</v>
+        <v>1860.94</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B37" s="15">
-        <f>(B36/('partidos regular'!$B$1-14))*100</f>
-        <v>61.016949152542374</v>
+        <v>170</v>
+      </c>
+      <c r="B37">
+        <v>2079.48</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="B38">
-        <f>SUM(B40:B45)</f>
-        <v>9485.18</v>
+        <v>2032.1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" s="14">
-        <f>B38/('partidos regular'!$B$1-14)</f>
-        <v>160.76576271186443</v>
+        <v>180</v>
+      </c>
+      <c r="B39">
+        <v>177.8</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>97</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B41">
-        <v>1662.36</v>
+        <f>COUNTIF('partidos regular'!A:A,"C*")</f>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B42">
-        <v>1787.3</v>
+        <v>93</v>
+      </c>
+      <c r="B42" s="15">
+        <f>(B41/('partidos regular'!$B$1-14))*100</f>
+        <v>48.35164835164835</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B43">
-        <v>2000.46</v>
+        <f>SUM(B45:B52)</f>
+        <v>11553.340000000002</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>167</v>
-      </c>
-      <c r="B44">
-        <v>1903.28</v>
+        <v>95</v>
+      </c>
+      <c r="B44" s="14">
+        <f>B43/('partidos regular'!$B$1-14)</f>
+        <v>126.95978021978024</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="B45">
-        <v>2131.7800000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="B46">
+        <v>1662.36</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B47">
-        <f>COUNTIF('partidos regular'!A:A,"G*")</f>
-        <v>37</v>
+        <v>1787.3</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="15">
-        <f>(B47/'partidos regular'!$B$1)*100</f>
-        <v>50.684931506849317</v>
+        <v>100</v>
+      </c>
+      <c r="B48">
+        <v>2000.46</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="B49">
-        <f>SUM(B51:B56)</f>
-        <v>11146.740000000002</v>
+        <v>1903.28</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" s="14">
-        <f>B49/'partidos regular'!$B$1</f>
-        <v>152.6950684931507</v>
+        <v>170</v>
+      </c>
+      <c r="B50">
+        <v>2131.7800000000002</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="B51">
-        <v>1535.92</v>
+        <v>1754.88</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="B52">
-        <v>2053.06</v>
+        <v>313.27999999999997</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53">
-        <v>1728.92</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B54">
-        <v>1896.22</v>
+        <f>COUNTIF('partidos regular'!A:A,"G*")</f>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>167</v>
-      </c>
-      <c r="B55">
-        <v>1954.92</v>
+        <v>93</v>
+      </c>
+      <c r="B55" s="15">
+        <f>(B54/'partidos regular'!$B$1)*100</f>
+        <v>48.571428571428569</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="B56">
-        <v>1977.7</v>
+        <f>SUM(B58:B65)</f>
+        <v>13685.36</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>95</v>
+      </c>
+      <c r="B57" s="14">
+        <f>B56/'partidos regular'!$B$1</f>
+        <v>130.33676190476191</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B58">
-        <f>COUNTIF('partidos regular'!A:A,"S*")</f>
-        <v>43</v>
+        <v>1535.92</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>93</v>
-      </c>
-      <c r="B59" s="15">
-        <f>(B58/'partidos regular'!$B$1)*100</f>
-        <v>58.904109589041099</v>
+        <v>98</v>
+      </c>
+      <c r="B59">
+        <v>2053.06</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B60">
-        <f>SUM(B62:B67)</f>
-        <v>11496.8</v>
+        <v>1728.92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>95</v>
-      </c>
-      <c r="B61" s="14">
-        <f>B60/'partidos regular'!$B$1</f>
-        <v>157.49041095890411</v>
+        <v>100</v>
+      </c>
+      <c r="B61">
+        <v>1896.22</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="B62">
-        <v>1499.98</v>
+        <v>1954.92</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="B63">
-        <v>1784.3</v>
+        <v>1977.7</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="B64">
-        <v>1937.3</v>
+        <v>2210.3000000000002</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="B65">
-        <v>2087.1</v>
+        <v>328.32</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>167</v>
-      </c>
-      <c r="B66">
-        <v>2164.12</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="B67">
-        <v>2024</v>
+        <f>COUNTIF('partidos regular'!A:A,"S*")</f>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>106</v>
+        <v>93</v>
+      </c>
+      <c r="B68" s="15">
+        <f>(B67/'partidos regular'!$B$1)*100</f>
+        <v>49.523809523809526</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B69">
-        <f>COUNTIF('partidos regular'!A:A,"N*")</f>
-        <v>43</v>
+        <f>SUM(B71:B78)</f>
+        <v>13737.48</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>93</v>
-      </c>
-      <c r="B70" s="15">
-        <f>(B69/'partidos regular'!$B$1)*100</f>
-        <v>58.904109589041099</v>
+        <v>95</v>
+      </c>
+      <c r="B70" s="14">
+        <f>B69/'partidos regular'!$B$1</f>
+        <v>130.83314285714286</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B71">
-        <f>SUM(B73:B78)</f>
-        <v>11533.36</v>
+        <v>1499.98</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>95</v>
-      </c>
-      <c r="B72" s="14">
-        <f>B71/'partidos regular'!$B$1</f>
-        <v>157.99123287671233</v>
+        <v>98</v>
+      </c>
+      <c r="B72">
+        <v>1784.3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B73">
-        <v>1623.6</v>
+        <v>1937.3</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B74">
-        <v>1888.78</v>
+        <v>2087.1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="B75">
-        <v>1828.58</v>
+        <v>2164.12</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="B76">
-        <v>2079.98</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B77">
-        <v>2116.6</v>
+        <v>1969.08</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B78">
-        <v>1995.82</v>
+        <v>271.60000000000002</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -3857,8 +4425,8 @@
         <v>92</v>
       </c>
       <c r="B80">
-        <f>COUNTIF('partidos regular'!A:A,"K*")</f>
-        <v>25</v>
+        <f>COUNTIF('partidos regular'!A:A,"N*")</f>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -3866,8 +4434,8 @@
         <v>93</v>
       </c>
       <c r="B81" s="15">
-        <f>(B80/('partidos regular'!$B$1-43))*100</f>
-        <v>83.333333333333343</v>
+        <f>(B80/'partidos regular'!$B$1)*100</f>
+        <v>46.666666666666664</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -3875,8 +4443,8 @@
         <v>94</v>
       </c>
       <c r="B82">
-        <f>SUM(B84:B89)</f>
-        <v>5932.84</v>
+        <f>SUM(B84:B91)</f>
+        <v>13740.18</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -3884,8 +4452,8 @@
         <v>95</v>
       </c>
       <c r="B83" s="14">
-        <f>B82/('partidos regular'!$B$1-43)</f>
-        <v>197.76133333333334</v>
+        <f>B82/'partidos regular'!$B$1</f>
+        <v>130.85885714285715</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -3893,7 +4461,7 @@
         <v>97</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1623.6</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -3901,7 +4469,7 @@
         <v>98</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1888.78</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -3909,7 +4477,7 @@
         <v>99</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1828.58</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -3917,7 +4485,7 @@
         <v>100</v>
       </c>
       <c r="B87">
-        <v>2024</v>
+        <v>2079.98</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -3925,7 +4493,7 @@
         <v>167</v>
       </c>
       <c r="B88">
-        <v>1915.14</v>
+        <v>2116.6</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -3933,10 +4501,132 @@
         <v>170</v>
       </c>
       <c r="B89">
+        <v>1995.82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90">
+        <v>1962.18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91">
+        <v>244.64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <f>COUNTIF('partidos regular'!A:A,"K*")</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" s="15">
+        <f>(B93/('partidos regular'!$B$1-43))*100</f>
+        <v>51.612903225806448</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <f>SUM(B97:B104)</f>
+        <v>7999.92</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14">
+        <f>B95/('partidos regular'!$B$1-43)</f>
+        <v>129.03096774193548</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+      <c r="B100">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>167</v>
+      </c>
+      <c r="B101">
+        <v>1915.14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>170</v>
+      </c>
+      <c r="B102">
         <v>1993.7</v>
       </c>
     </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>177</v>
+      </c>
+      <c r="B103">
+        <v>1752.22</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>180</v>
+      </c>
+      <c r="B104">
+        <v>314.86</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3958,7 +4648,7 @@
       </c>
       <c r="B2" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EG")+COUNTIF(playoffs!A:A,"EG")+COUNTIF(playoffs!E:E,"EG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GE")+COUNTIF(playoffs!A:A,"GE")+COUNTIF(playoffs!E:E,"GE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EG")+COUNTIF(playoffs!E:E,"EG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GE")+COUNTIF(playoffs!E:E,"GE")&amp;")"</f>
-        <v>8-4 (0-0)</v>
+        <v>8-6 (0-0)</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3967,7 +4657,7 @@
       </c>
       <c r="B3" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"ES")+COUNTIF(playoffs!A:A,"ES")+COUNTIF(playoffs!E:E,"ES")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SE")+COUNTIF(playoffs!A:A,"SE")+COUNTIF(playoffs!E:E,"SE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"ES")+COUNTIF(playoffs!E:E,"ES")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SE")+COUNTIF(playoffs!E:E,"SE")&amp;")"</f>
-        <v>6-7 (0-1)</v>
+        <v>6-9 (0-1)</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3976,7 +4666,7 @@
       </c>
       <c r="B4" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EN")+COUNTIF(playoffs!A:A,"EN")+COUNTIF(playoffs!E:E,"EN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NE")+COUNTIF(playoffs!A:A,"NE")+COUNTIF(playoffs!E:E,"GE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EN")+COUNTIF(playoffs!E:E,"EN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NE")+COUNTIF(playoffs!E:E,"NE")&amp;")"</f>
-        <v>7-5 (0-0)</v>
+        <v>9-6 (0-0)</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3985,7 +4675,7 @@
       </c>
       <c r="B5" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EL")+COUNTIF(playoffs!A:A,"EL")+COUNTIF(playoffs!E:E,"EL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LE")+COUNTIF(playoffs!A:A,"LE")+COUNTIF(playoffs!E:E,"LE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EL")+COUNTIF(playoffs!E:E,"EL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LE")+COUNTIF(playoffs!E:E,"LE")&amp;")"</f>
-        <v>8-4 (0-0)</v>
+        <v>8-6 (0-0)</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3994,7 +4684,7 @@
       </c>
       <c r="B6" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EC")+COUNTIF(playoffs!A:A,"EC")+COUNTIF(playoffs!E:E,"EC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CE")+COUNTIF(playoffs!A:A,"CE")+COUNTIF(playoffs!E:E,"CE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EC")+COUNTIF(playoffs!E:E,"EC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CE")+COUNTIF(playoffs!E:E,"CE")&amp;")"</f>
-        <v>4-7 (0-0)</v>
+        <v>5-8 (0-0)</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4003,7 +4693,7 @@
       </c>
       <c r="B7" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EK")+COUNTIF(playoffs!A:A,"EK")+COUNTIF(playoffs!E:E,"EK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KE")+COUNTIF(playoffs!A:A,"KE")+COUNTIF(playoffs!E:E,"KE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EK")+COUNTIF(playoffs!E:E,"EK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KE")+COUNTIF(playoffs!E:E,"KE")&amp;")"</f>
-        <v>3-6 (1-0)</v>
+        <v>5-8 (1-0)</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4012,7 +4702,7 @@
       </c>
       <c r="B8" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"EJ")+COUNTIF(playoffs!A:A,"EJ")+COUNTIF(playoffs!E:E,"EJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JE")+COUNTIF(playoffs!A:A,"JE")+COUNTIF(playoffs!E:E,"JE")&amp;" ("&amp;COUNTIF(playoffs!A:A,"EJ")+COUNTIF(playoffs!E:E,"EJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JE")+COUNTIF(playoffs!E:E,"JE")&amp;")"</f>
-        <v>8-6 (1-1)</v>
+        <v>8-8 (1-1)</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4036,7 +4726,7 @@
       </c>
       <c r="B12" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GE")+COUNTIF(playoffs!A:A,"GE")+COUNTIF(playoffs!E:E,"GE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EG")+COUNTIF(playoffs!A:A,"EG")+COUNTIF(playoffs!E:E,"EG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GE")+COUNTIF(playoffs!E:E,"GE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EG")+COUNTIF(playoffs!E:E,"EG")&amp;")"</f>
-        <v>4-8 (0-0)</v>
+        <v>6-8 (0-0)</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4045,7 +4735,7 @@
       </c>
       <c r="B13" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GS")+COUNTIF(playoffs!A:A,"GS")+COUNTIF(playoffs!E:E,"GS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SG")+COUNTIF(playoffs!A:A,"SG")+COUNTIF(playoffs!E:E,"SG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GS")+COUNTIF(playoffs!E:E,"GS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SG")+COUNTIF(playoffs!E:E,"SG")&amp;")"</f>
-        <v>6-6 (0-0)</v>
+        <v>9-7 (1-0)</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4054,7 +4744,7 @@
       </c>
       <c r="B14" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GN")+COUNTIF(playoffs!A:A,"GN")+COUNTIF(playoffs!E:E,"GN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NG")+COUNTIF(playoffs!A:A,"NG")+COUNTIF(playoffs!E:E,"NG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GN")+COUNTIF(playoffs!E:E,"GN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NG")+COUNTIF(playoffs!E:E,"NG")&amp;")"</f>
-        <v>6-11 (1-0)</v>
+        <v>9-11 (1-0)</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -4063,7 +4753,7 @@
       </c>
       <c r="B15" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GL")+COUNTIF(playoffs!A:A,"GL")+COUNTIF(playoffs!E:E,"GL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LG")+COUNTIF(playoffs!A:A,"LG")+COUNTIF(playoffs!E:E,"LG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GL")+COUNTIF(playoffs!E:E,"GL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LG")+COUNTIF(playoffs!E:E,"LG")&amp;")"</f>
-        <v>7-6 (0-1)</v>
+        <v>9-6 (0-1)</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -4072,7 +4762,7 @@
       </c>
       <c r="B16" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GC")+COUNTIF(playoffs!A:A,"GC")+COUNTIF(playoffs!E:E,"GC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CG")+COUNTIF(playoffs!A:A,"CG")+COUNTIF(playoffs!E:E,"CG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GC")+COUNTIF(playoffs!E:E,"GC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CG")+COUNTIF(playoffs!E:E,"CG")&amp;")"</f>
-        <v>3-7 (0-0)</v>
+        <v>5-7 (0-0)</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4081,7 +4771,7 @@
       </c>
       <c r="B17" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GK")+COUNTIF(playoffs!A:A,"GK")+COUNTIF(playoffs!E:E,"GK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KG")+COUNTIF(playoffs!A:A,"KG")+COUNTIF(playoffs!E:E,"KG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GK")+COUNTIF(playoffs!E:E,"GK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KG")+COUNTIF(playoffs!E:E,"KG")&amp;")"</f>
-        <v>4-2 (0-0)</v>
+        <v>6-2 (0-0)</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +4780,7 @@
       </c>
       <c r="B18" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"GJ")+COUNTIF(playoffs!A:A,"GJ")+COUNTIF(playoffs!E:E,"GJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JG")+COUNTIF(playoffs!A:A,"JG")+COUNTIF(playoffs!E:E,"JG")&amp;" ("&amp;COUNTIF(playoffs!A:A,"GJ")+COUNTIF(playoffs!E:E,"GJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JG")+COUNTIF(playoffs!E:E,"JG")&amp;")"</f>
-        <v>4-9 (1-0)</v>
+        <v>5-13 (1-2)</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -4114,7 +4804,7 @@
       </c>
       <c r="B22" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SE")+COUNTIF(playoffs!A:A,"SE")+COUNTIF(playoffs!E:E,"SE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"ES")+COUNTIF(playoffs!A:A,"ES")+COUNTIF(playoffs!E:E,"ES")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SE")+COUNTIF(playoffs!E:E,"SE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"ES")+COUNTIF(playoffs!E:E,"ES")&amp;")"</f>
-        <v>7-6 (1-0)</v>
+        <v>9-6 (1-0)</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -4123,7 +4813,7 @@
       </c>
       <c r="B23" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SG")+COUNTIF(playoffs!A:A,"SG")+COUNTIF(playoffs!E:E,"SG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GS")+COUNTIF(playoffs!A:A,"GS")+COUNTIF(playoffs!E:E,"GS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SG")+COUNTIF(playoffs!E:E,"SG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GS")+COUNTIF(playoffs!E:E,"GS")&amp;")"</f>
-        <v>6-6 (0-0)</v>
+        <v>7-9 (0-1)</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4132,7 +4822,7 @@
       </c>
       <c r="B24" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SN")+COUNTIF(playoffs!A:A,"SN")+COUNTIF(playoffs!E:E,"SN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NS")+COUNTIF(playoffs!A:A,"NS")+COUNTIF(playoffs!E:E,"NS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SN")+COUNTIF(playoffs!E:E,"SN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NS")+COUNTIF(playoffs!E:E,"NS")&amp;")"</f>
-        <v>5-7 (0-0)</v>
+        <v>6-8 (0-0)</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -4141,7 +4831,7 @@
       </c>
       <c r="B25" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SL")+COUNTIF(playoffs!A:A,"SL")+COUNTIF(playoffs!E:E,"SL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LS")+COUNTIF(playoffs!A:A,"LS")+COUNTIF(playoffs!E:E,"LS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SL")+COUNTIF(playoffs!E:E,"SL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LS")+COUNTIF(playoffs!E:E,"LS")&amp;")"</f>
-        <v>8-6 (1-0)</v>
+        <v>9-9 (1-1)</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -4150,7 +4840,7 @@
       </c>
       <c r="B26" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SC")+COUNTIF(playoffs!A:A,"SC")+COUNTIF(playoffs!E:E,"SC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CS")+COUNTIF(playoffs!A:A,"CS")+COUNTIF(playoffs!E:E,"CS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SC")+COUNTIF(playoffs!E:E,"SC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CS")+COUNTIF(playoffs!E:E,"CS")&amp;")"</f>
-        <v>6-4 (0-0)</v>
+        <v>6-6 (0-0)</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -4159,7 +4849,7 @@
       </c>
       <c r="B27" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SK")+COUNTIF(playoffs!A:A,"SK")+COUNTIF(playoffs!E:E,"SK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KS")+COUNTIF(playoffs!A:A,"KS")+COUNTIF(playoffs!E:E,"KS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SK")+COUNTIF(playoffs!E:E,"SK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KS")+COUNTIF(playoffs!E:E,"KS")&amp;")"</f>
-        <v>3-3 (0-0)</v>
+        <v>5-3 (0-0)</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -4168,7 +4858,7 @@
       </c>
       <c r="B28" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"SJ")+COUNTIF(playoffs!A:A,"SJ")+COUNTIF(playoffs!E:E,"SJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JS")+COUNTIF(playoffs!A:A,"JS")+COUNTIF(playoffs!E:E,"JS")&amp;" ("&amp;COUNTIF(playoffs!A:A,"SJ")+COUNTIF(playoffs!E:E,"SJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JS")+COUNTIF(playoffs!E:E,"JS")&amp;")"</f>
-        <v>6-10 (0-1)</v>
+        <v>8-11 (0-1)</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -4183,7 +4873,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -4192,7 +4882,7 @@
       </c>
       <c r="B32" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NE")+COUNTIF(playoffs!A:A,"NE")+COUNTIF(playoffs!E:E,"NE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EN")+COUNTIF(playoffs!A:A,"EN")+COUNTIF(playoffs!E:E,"EN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NE")+COUNTIF(playoffs!E:E,"NE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EN")+COUNTIF(playoffs!E:E,"EN")&amp;")"</f>
-        <v>5-7 (0-0)</v>
+        <v>6-9 (0-0)</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -4201,7 +4891,7 @@
       </c>
       <c r="B33" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NG")+COUNTIF(playoffs!A:A,"NG")+COUNTIF(playoffs!E:E,"NG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GN")+COUNTIF(playoffs!A:A,"GN")+COUNTIF(playoffs!E:E,"GN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NG")+COUNTIF(playoffs!E:E,"NG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GN")+COUNTIF(playoffs!E:E,"GN")&amp;")"</f>
-        <v>11-6 (0-1)</v>
+        <v>11-9 (0-1)</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +4900,7 @@
       </c>
       <c r="B34" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NS")+COUNTIF(playoffs!A:A,"NS")+COUNTIF(playoffs!E:E,"NS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SN")+COUNTIF(playoffs!A:A,"SN")+COUNTIF(playoffs!E:E,"SN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NS")+COUNTIF(playoffs!E:E,"NS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SN")+COUNTIF(playoffs!E:E,"SN")&amp;")"</f>
-        <v>7-5 (0-0)</v>
+        <v>8-6 (0-0)</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -4219,7 +4909,7 @@
       </c>
       <c r="B35" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NL")+COUNTIF(playoffs!A:A,"NL")+COUNTIF(playoffs!E:E,"NL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LN")+COUNTIF(playoffs!A:A,"LN")+COUNTIF(playoffs!E:E,"LN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NL")+COUNTIF(playoffs!E:E,"NL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LN")+COUNTIF(playoffs!E:E,"LN")&amp;")"</f>
-        <v>2-9 (0-0)</v>
+        <v>3-10 (0-0)</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -4228,7 +4918,7 @@
       </c>
       <c r="B36" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NC")+COUNTIF(playoffs!A:A,"NC")+COUNTIF(playoffs!E:E,"NC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CN")+COUNTIF(playoffs!A:A,"CN")+COUNTIF(playoffs!E:E,"CN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NC")+COUNTIF(playoffs!E:E,"NC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CN")+COUNTIF(playoffs!E:E,"CN")&amp;")"</f>
-        <v>6-5 (1-0)</v>
+        <v>8-6 (1-0)</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -4237,7 +4927,7 @@
       </c>
       <c r="B37" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NK")+COUNTIF(playoffs!A:A,"NK")+COUNTIF(playoffs!E:E,"NK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KN")+COUNTIF(playoffs!A:A,"KN")+COUNTIF(playoffs!E:E,"KN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NK")+COUNTIF(playoffs!E:E,"NK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KN")+COUNTIF(playoffs!E:E,"KN")&amp;")"</f>
-        <v>2-5 (0-1)</v>
+        <v>3-6 (0-1)</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4936,7 @@
       </c>
       <c r="B38" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"NJ")+COUNTIF(playoffs!A:A,"NJ")+COUNTIF(playoffs!E:E,"NJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JN")+COUNTIF(playoffs!A:A,"JN")+COUNTIF(playoffs!E:E,"JN")&amp;" ("&amp;COUNTIF(playoffs!A:A,"NJ")+COUNTIF(playoffs!E:E,"NJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JN")+COUNTIF(playoffs!E:E,"JN")&amp;")"</f>
-        <v>7-6 (0-1)</v>
+        <v>7-8 (0-1)</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -4270,7 +4960,7 @@
       </c>
       <c r="B42" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LE")+COUNTIF(playoffs!A:A,"LE")+COUNTIF(playoffs!E:E,"LE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EL")+COUNTIF(playoffs!A:A,"EL")+COUNTIF(playoffs!E:E,"EL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LE")+COUNTIF(playoffs!E:E,"LE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EL")+COUNTIF(playoffs!E:E,"EL")&amp;")"</f>
-        <v>4-8 (0-0)</v>
+        <v>6-8 (0-0)</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -4279,7 +4969,7 @@
       </c>
       <c r="B43" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LG")+COUNTIF(playoffs!A:A,"LG")+COUNTIF(playoffs!E:E,"LG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GL")+COUNTIF(playoffs!A:A,"GL")+COUNTIF(playoffs!E:E,"GL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LG")+COUNTIF(playoffs!E:E,"LG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GL")+COUNTIF(playoffs!E:E,"GL")&amp;")"</f>
-        <v>6-7 (1-0)</v>
+        <v>6-9 (1-0)</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -4288,7 +4978,7 @@
       </c>
       <c r="B44" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LS")+COUNTIF(playoffs!A:A,"LS")+COUNTIF(playoffs!E:E,"LS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SL")+COUNTIF(playoffs!A:A,"SL")+COUNTIF(playoffs!E:E,"SL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LS")+COUNTIF(playoffs!E:E,"LS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SL")+COUNTIF(playoffs!E:E,"SL")&amp;")"</f>
-        <v>6-8 (0-1)</v>
+        <v>9-9 (1-1)</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -4297,7 +4987,7 @@
       </c>
       <c r="B45" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LN")+COUNTIF(playoffs!A:A,"LN")+COUNTIF(playoffs!E:E,"LN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NL")+COUNTIF(playoffs!A:A,"NL")+COUNTIF(playoffs!E:E,"NL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LN")+COUNTIF(playoffs!E:E,"LN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NL")+COUNTIF(playoffs!E:E,"NL")&amp;")"</f>
-        <v>9-2 (0-0)</v>
+        <v>10-3 (0-0)</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -4306,7 +4996,7 @@
       </c>
       <c r="B46" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LC")+COUNTIF(playoffs!A:A,"LC")+COUNTIF(playoffs!E:E,"LC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CL")+COUNTIF(playoffs!A:A,"CL")+COUNTIF(playoffs!E:E,"CL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LC")+COUNTIF(playoffs!E:E,"LC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CL")+COUNTIF(playoffs!E:E,"CL")&amp;")"</f>
-        <v>6-8 (0-0)</v>
+        <v>8-10 (0-0)</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -4315,7 +5005,7 @@
       </c>
       <c r="B47" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LK")+COUNTIF(playoffs!A:A,"LK")+COUNTIF(playoffs!E:E,"LK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KL")+COUNTIF(playoffs!A:A,"KL")+COUNTIF(playoffs!E:E,"KL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LK")+COUNTIF(playoffs!E:E,"LK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KL")+COUNTIF(playoffs!E:E,"KL")&amp;")"</f>
-        <v>2-4 (0-0)</v>
+        <v>3-5 (0-0)</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -4324,7 +5014,7 @@
       </c>
       <c r="B48" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"LJ")+COUNTIF(playoffs!A:A,"LJ")+COUNTIF(playoffs!E:E,"LJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JL")+COUNTIF(playoffs!A:A,"JL")+COUNTIF(playoffs!E:E,"JL")&amp;" ("&amp;COUNTIF(playoffs!A:A,"LJ")+COUNTIF(playoffs!E:E,"LJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JL")+COUNTIF(playoffs!E:E,"JL")&amp;")"</f>
-        <v>5-8 (1-0)</v>
+        <v>6-11 (2-1)</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -4348,7 +5038,7 @@
       </c>
       <c r="B52" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CE")+COUNTIF(playoffs!A:A,"CE")+COUNTIF(playoffs!E:E,"CE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EC")+COUNTIF(playoffs!A:A,"EC")+COUNTIF(playoffs!E:E,"EC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CE")+COUNTIF(playoffs!E:E,"CE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EC")+COUNTIF(playoffs!E:E,"EC")&amp;")"</f>
-        <v>7-4 (0-0)</v>
+        <v>8-5 (0-0)</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -4357,7 +5047,7 @@
       </c>
       <c r="B53" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CG")+COUNTIF(playoffs!A:A,"CG")+COUNTIF(playoffs!E:E,"CG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GC")+COUNTIF(playoffs!A:A,"GC")+COUNTIF(playoffs!E:E,"GC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CG")+COUNTIF(playoffs!E:E,"CG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GC")+COUNTIF(playoffs!E:E,"GC")&amp;")"</f>
-        <v>7-3 (0-0)</v>
+        <v>7-5 (0-0)</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -4366,7 +5056,7 @@
       </c>
       <c r="B54" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CS")+COUNTIF(playoffs!A:A,"CS")+COUNTIF(playoffs!E:E,"CS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SC")+COUNTIF(playoffs!A:A,"SC")+COUNTIF(playoffs!E:E,"SC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CS")+COUNTIF(playoffs!E:E,"CS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SC")+COUNTIF(playoffs!E:E,"SC")&amp;")"</f>
-        <v>4-6 (0-0)</v>
+        <v>6-6 (0-0)</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -4375,7 +5065,7 @@
       </c>
       <c r="B55" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CN")+COUNTIF(playoffs!A:A,"CN")+COUNTIF(playoffs!E:E,"CN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NC")+COUNTIF(playoffs!A:A,"NC")+COUNTIF(playoffs!E:E,"NC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CN")+COUNTIF(playoffs!E:E,"CN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NC")+COUNTIF(playoffs!E:E,"NC")&amp;")"</f>
-        <v>5-6 (0-1)</v>
+        <v>6-8 (0-1)</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -4384,7 +5074,7 @@
       </c>
       <c r="B56" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CL")+COUNTIF(playoffs!A:A,"CL")+COUNTIF(playoffs!E:E,"CL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LC")+COUNTIF(playoffs!A:A,"LC")+COUNTIF(playoffs!E:E,"LC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CL")+COUNTIF(playoffs!E:E,"CL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LC")+COUNTIF(playoffs!E:E,"LC")&amp;")"</f>
-        <v>8-6 (0-0)</v>
+        <v>10-8 (0-0)</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -4393,7 +5083,7 @@
       </c>
       <c r="B57" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CK")+COUNTIF(playoffs!A:A,"CK")+COUNTIF(playoffs!E:E,"CK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KC")+COUNTIF(playoffs!A:A,"KC")+COUNTIF(playoffs!E:E,"KC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CK")+COUNTIF(playoffs!E:E,"CK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KC")+COUNTIF(playoffs!E:E,"KC")&amp;")"</f>
-        <v>2-4 (0-0)</v>
+        <v>2-6 (0-0)</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -4402,7 +5092,7 @@
       </c>
       <c r="B58" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"CJ")+COUNTIF(playoffs!A:A,"CJ")+COUNTIF(playoffs!E:E,"CJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JC")+COUNTIF(playoffs!A:A,"JC")+COUNTIF(playoffs!E:E,"JC")&amp;" ("&amp;COUNTIF(playoffs!A:A,"CJ")+COUNTIF(playoffs!E:E,"CJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JC")+COUNTIF(playoffs!E:E,"JC")&amp;")"</f>
-        <v>2-8 (0-0)</v>
+        <v>4-8 (0-0)</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -4426,7 +5116,7 @@
       </c>
       <c r="B62" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KE")+COUNTIF(playoffs!A:A,"KE")+COUNTIF(playoffs!E:E,"KE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EK")+COUNTIF(playoffs!A:A,"EK")+COUNTIF(playoffs!E:E,"EK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KE")+COUNTIF(playoffs!E:E,"KE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EK")+COUNTIF(playoffs!E:E,"EK")&amp;")"</f>
-        <v>6-3 (0-1)</v>
+        <v>8-5 (0-1)</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -4435,7 +5125,7 @@
       </c>
       <c r="B63" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KG")+COUNTIF(playoffs!A:A,"KG")+COUNTIF(playoffs!E:E,"KG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GK")+COUNTIF(playoffs!A:A,"GK")+COUNTIF(playoffs!E:E,"GK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KG")+COUNTIF(playoffs!E:E,"KG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GK")+COUNTIF(playoffs!E:E,"GK")&amp;")"</f>
-        <v>2-4 (0-0)</v>
+        <v>2-6 (0-0)</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -4444,7 +5134,7 @@
       </c>
       <c r="B64" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KS")+COUNTIF(playoffs!A:A,"KS")+COUNTIF(playoffs!E:E,"KS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SK")+COUNTIF(playoffs!A:A,"SK")+COUNTIF(playoffs!E:E,"SK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KS")+COUNTIF(playoffs!E:E,"KS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SK")+COUNTIF(playoffs!E:E,"SK")&amp;")"</f>
-        <v>3-3 (0-0)</v>
+        <v>3-5 (0-0)</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -4453,7 +5143,7 @@
       </c>
       <c r="B65" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KN")+COUNTIF(playoffs!A:A,"KN")+COUNTIF(playoffs!E:E,"KN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NK")+COUNTIF(playoffs!A:A,"NK")+COUNTIF(playoffs!E:E,"NK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KN")+COUNTIF(playoffs!E:E,"KN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NK")+COUNTIF(playoffs!E:E,"NK")&amp;")"</f>
-        <v>5-2 (1-0)</v>
+        <v>6-3 (1-0)</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -4462,7 +5152,7 @@
       </c>
       <c r="B66" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KL")+COUNTIF(playoffs!A:A,"KL")+COUNTIF(playoffs!E:E,"KL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LK")+COUNTIF(playoffs!A:A,"LK")+COUNTIF(playoffs!E:E,"LK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KL")+COUNTIF(playoffs!E:E,"KL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LK")+COUNTIF(playoffs!E:E,"LK")&amp;")"</f>
-        <v>4-2 (0-0)</v>
+        <v>5-3 (0-0)</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -4471,7 +5161,7 @@
       </c>
       <c r="B67" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KC")+COUNTIF(playoffs!A:A,"KC")+COUNTIF(playoffs!E:E,"KC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CK")+COUNTIF(playoffs!A:A,"CK")+COUNTIF(playoffs!E:E,"CK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KC")+COUNTIF(playoffs!E:E,"KC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CK")+COUNTIF(playoffs!E:E,"CK")&amp;")"</f>
-        <v>4-2 (0-0)</v>
+        <v>6-2 (0-0)</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -4480,7 +5170,7 @@
       </c>
       <c r="B68" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"KJ")+COUNTIF(playoffs!A:A,"KJ")+COUNTIF(playoffs!E:E,"KJ")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"JK")+COUNTIF(playoffs!A:A,"JK")+COUNTIF(playoffs!E:E,"JK")&amp;" ("&amp;COUNTIF(playoffs!A:A,"KJ")+COUNTIF(playoffs!E:E,"KJ")&amp;"-"&amp;COUNTIF(playoffs!A:A,"JK")+COUNTIF(playoffs!E:E,"JK")&amp;")"</f>
-        <v>2-5 (0-0)</v>
+        <v>3-7 (0-0)</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -4504,7 +5194,7 @@
       </c>
       <c r="B72" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JE")+COUNTIF(playoffs!A:A,"JE")+COUNTIF(playoffs!E:E,"JE")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"EJ")+COUNTIF(playoffs!A:A,"EJ")+COUNTIF(playoffs!E:E,"EJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JE")+COUNTIF(playoffs!E:E,"JE")&amp;"-"&amp;COUNTIF(playoffs!A:A,"EJ")+COUNTIF(playoffs!E:E,"EJ")&amp;")"</f>
-        <v>6-8 (1-1)</v>
+        <v>8-8 (1-1)</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -4513,7 +5203,7 @@
       </c>
       <c r="B73" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JG")+COUNTIF(playoffs!A:A,"JG")+COUNTIF(playoffs!E:E,"JG")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"GJ")+COUNTIF(playoffs!A:A,"GJ")+COUNTIF(playoffs!E:E,"GJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JG")+COUNTIF(playoffs!E:E,"JG")&amp;"-"&amp;COUNTIF(playoffs!A:A,"GJ")+COUNTIF(playoffs!E:E,"GJ")&amp;")"</f>
-        <v>9-4 (0-1)</v>
+        <v>13-5 (2-1)</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -4522,7 +5212,7 @@
       </c>
       <c r="B74" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JS")+COUNTIF(playoffs!A:A,"JS")+COUNTIF(playoffs!E:E,"JS")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"SJ")+COUNTIF(playoffs!A:A,"SJ")+COUNTIF(playoffs!E:E,"SJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JS")+COUNTIF(playoffs!E:E,"JS")&amp;"-"&amp;COUNTIF(playoffs!A:A,"SJ")+COUNTIF(playoffs!E:E,"SJ")&amp;")"</f>
-        <v>10-6 (1-0)</v>
+        <v>11-8 (1-0)</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -4531,7 +5221,7 @@
       </c>
       <c r="B75" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JN")+COUNTIF(playoffs!A:A,"JN")+COUNTIF(playoffs!E:E,"JN")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"NJ")+COUNTIF(playoffs!A:A,"NJ")+COUNTIF(playoffs!E:E,"NJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JN")+COUNTIF(playoffs!E:E,"JN")&amp;"-"&amp;COUNTIF(playoffs!A:A,"NJ")+COUNTIF(playoffs!E:E,"NJ")&amp;")"</f>
-        <v>6-7 (1-0)</v>
+        <v>8-7 (1-0)</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -4540,7 +5230,7 @@
       </c>
       <c r="B76" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JL")+COUNTIF(playoffs!A:A,"JL")+COUNTIF(playoffs!E:E,"JL")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"LJ")+COUNTIF(playoffs!A:A,"LJ")+COUNTIF(playoffs!E:E,"LJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JL")+COUNTIF(playoffs!E:E,"JL")&amp;"-"&amp;COUNTIF(playoffs!A:A,"LJ")+COUNTIF(playoffs!E:E,"LJ")&amp;")"</f>
-        <v>8-5 (0-1)</v>
+        <v>11-6 (1-2)</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -4549,7 +5239,7 @@
       </c>
       <c r="B77" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JC")+COUNTIF(playoffs!A:A,"JC")+COUNTIF(playoffs!E:E,"JC")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"CJ")+COUNTIF(playoffs!A:A,"CJ")+COUNTIF(playoffs!E:E,"CJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JC")+COUNTIF(playoffs!E:E,"JC")&amp;"-"&amp;COUNTIF(playoffs!A:A,"CJ")+COUNTIF(playoffs!E:E,"CJ")&amp;")"</f>
-        <v>8-2 (0-0)</v>
+        <v>8-4 (0-0)</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -4558,7 +5248,7 @@
       </c>
       <c r="B78" t="str">
         <f xml:space="preserve"> COUNTIF('partidos regular'!A:A,"JK")+COUNTIF(playoffs!A:A,"JK")+COUNTIF(playoffs!E:E,"JK")&amp;"-"&amp;COUNTIF('partidos regular'!A:A,"KJ")+COUNTIF(playoffs!A:A,"KJ")+COUNTIF(playoffs!E:E,"KJ")&amp;" ("&amp;COUNTIF(playoffs!A:A,"JK")+COUNTIF(playoffs!E:E,"JK")&amp;"-"&amp;COUNTIF(playoffs!A:A,"KJ")+COUNTIF(playoffs!E:E,"KJ")&amp;")"</f>
-        <v>5-2 (0-0)</v>
+        <v>7-3 (0-0)</v>
       </c>
     </row>
   </sheetData>
@@ -4580,8 +5270,8 @@
         <v>107</v>
       </c>
       <c r="B2" s="14">
-        <f>(stats!$B$80*10+COUNTIF(playoffs!E:E,"*K*")*10+COUNTIF(playoffs!B:B,"K")*25+COUNTIF(playoffs!C:C,"K")*20+COUNTIF(playoffs!E:E,"K*")*30+(stats!$B$82/250)-COUNTIF(playoffs!D:D,"K")*15)/('partidos regular'!$B$1-43)</f>
-        <v>10.291045333333333</v>
+        <f>(stats!$B$93*10+COUNTIF(playoffs!E:E,"*K*")*10+COUNTIF(playoffs!B:B,"K")*25+COUNTIF(playoffs!C:C,"K")*20+COUNTIF(playoffs!E:E,"K*")*30+(stats!$B$95/250)-COUNTIF(playoffs!D:D,"K")*15)/('partidos regular'!$B$1-43)</f>
+        <v>5.7580593548387098</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4590,7 +5280,7 @@
       </c>
       <c r="B3" s="14">
         <f>(stats!$B$2*10+COUNTIF(playoffs!E:E,"*E*")*10+COUNTIF(playoffs!B:B,"E")*25+COUNTIF(playoffs!C:C,"E")*20+COUNTIF(playoffs!E:E,"E*")*30+(stats!$B$4/250)-COUNTIF(playoffs!D:D,"E")*15)/('partidos regular'!$B$1)</f>
-        <v>8.9463386301369869</v>
+        <v>6.4109805714285715</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -4598,8 +5288,8 @@
         <v>101</v>
       </c>
       <c r="B4" s="14">
-        <f>(stats!$B$14*10+COUNTIF(playoffs!E:E,"*J*")*10+COUNTIF(playoffs!B:B,"J")*25+COUNTIF(playoffs!C:C,"J")*20+COUNTIF(playoffs!E:E,"J*")*30+(stats!B16/250)-COUNTIF(playoffs!D:D,"J")*15)/('partidos regular'!$B$1)</f>
-        <v>9.4849490410958914</v>
+        <f>(stats!$B$15*10+COUNTIF(playoffs!E:E,"*J*")*10+COUNTIF(playoffs!B:B,"J")*25+COUNTIF(playoffs!C:C,"J")*20+COUNTIF(playoffs!E:E,"J*")*30+(stats!B17/250)-COUNTIF(playoffs!D:D,"J")*15)/('partidos regular'!$B$1)</f>
+        <v>8.6875436190476201</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4607,8 +5297,8 @@
         <v>102</v>
       </c>
       <c r="B5" s="14">
-        <f>(stats!$B$25*10+COUNTIF(playoffs!E:E,"*L*")*10+COUNTIF(playoffs!B:B,"L")*25+COUNTIF(playoffs!C:C,"L")*20+COUNTIF(playoffs!E:E,"L*")*30+(stats!$B$27/250)-COUNTIF(playoffs!D:D,"L")*15)/('partidos regular'!$B$1)</f>
-        <v>7.5979627397260279</v>
+        <f>(stats!$B$28*10+COUNTIF(playoffs!E:E,"*L*")*10+COUNTIF(playoffs!B:B,"L")*25+COUNTIF(playoffs!C:C,"L")*20+COUNTIF(playoffs!E:E,"L*")*30+(stats!$B$30/250)-COUNTIF(playoffs!D:D,"L")*15)/('partidos regular'!$B$1)</f>
+        <v>6.9380083809523807</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -4616,17 +5306,17 @@
         <v>105</v>
       </c>
       <c r="B6" s="14">
-        <f>(stats!$B$58*10+COUNTIF(playoffs!E:E,"*S*")*10+COUNTIF(playoffs!B:B,"S")*25+COUNTIF(playoffs!C:C,"S")*20+COUNTIF(playoffs!E:E,"S*")*30+(stats!B60/250)-COUNTIF(playoffs!D:D,"S")*15)/('partidos regular'!$B$1)</f>
-        <v>7.2737972602739731</v>
+        <f>(stats!$B$67*10+COUNTIF(playoffs!E:E,"*S*")*10+COUNTIF(playoffs!B:B,"S")*25+COUNTIF(playoffs!C:C,"S")*20+COUNTIF(playoffs!E:E,"S*")*30+(stats!B69/250)-COUNTIF(playoffs!D:D,"S")*15)/('partidos regular'!$B$1)</f>
+        <v>6.3804754285714287</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="B7" s="14">
-        <f>(stats!$B$69*10+COUNTIF(playoffs!E:E,"*N*")*10+COUNTIF(playoffs!B:B,"N")*25+COUNTIF(playoffs!C:C,"N")*20+COUNTIF(playoffs!E:E,"N*")*30+(stats!B71/250)-COUNTIF(playoffs!D:D,"N")*15)/('partidos regular'!$B$1)</f>
-        <v>7.3442936986301364</v>
+        <f>(stats!$B$80*10+COUNTIF(playoffs!E:E,"*N*")*10+COUNTIF(playoffs!B:B,"N")*25+COUNTIF(playoffs!C:C,"N")*20+COUNTIF(playoffs!E:E,"N*")*30+(stats!B82/250)-COUNTIF(playoffs!D:D,"N")*15)/('partidos regular'!$B$1)</f>
+        <v>5.7615306666666672</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4634,8 +5324,8 @@
         <v>104</v>
       </c>
       <c r="B8" s="14">
-        <f>(stats!$B$47*10+COUNTIF(playoffs!E:E,"*G*")*10+COUNTIF(playoffs!B:B,"G")*25+COUNTIF(playoffs!C:C,"G")*20+COUNTIF(playoffs!E:E,"G*")*30+(stats!B49/250)-COUNTIF(playoffs!D:D,"G")*15)/('partidos regular'!$B$1)</f>
-        <v>6.2272186301369858</v>
+        <f>(stats!$B$54*10+COUNTIF(playoffs!E:E,"*G*")*10+COUNTIF(playoffs!B:B,"G")*25+COUNTIF(playoffs!C:C,"G")*20+COUNTIF(playoffs!E:E,"G*")*30+(stats!B56/250)-COUNTIF(playoffs!D:D,"G")*15)/('partidos regular'!$B$1)</f>
+        <v>6.2832518095238097</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4643,8 +5333,8 @@
         <v>103</v>
       </c>
       <c r="B9" s="14">
-        <f>(stats!$B$36*10+COUNTIF(playoffs!E:E,"*C*")*10+COUNTIF(playoffs!B:B,"C")*25+COUNTIF(playoffs!C:C,"C")*20+COUNTIF(playoffs!E:E,"C*")*30+(stats!B38/250)-COUNTIF(playoffs!D:D,"C")*15)/(('partidos regular'!$B$1)-14)</f>
-        <v>6.8295037288135596</v>
+        <f>(stats!$B$41*10+COUNTIF(playoffs!E:E,"*C*")*10+COUNTIF(playoffs!B:B,"C")*25+COUNTIF(playoffs!C:C,"C")*20+COUNTIF(playoffs!E:E,"C*")*30+(stats!B43/250)-COUNTIF(playoffs!D:D,"C")*15)/(('partidos regular'!$B$1)-14)</f>
+        <v>5.3979490109890111</v>
       </c>
     </row>
   </sheetData>
